--- a/public/samples/university_feilds.xlsx
+++ b/public/samples/university_feilds.xlsx
@@ -1,34 +1,190 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NextSAAS\agencies\public\samples\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D938CB-17E8-43F9-AF98-7E561B319A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Universities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Universities" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
+  <si>
+    <t>university</t>
+  </si>
+  <si>
+    <t>partner_type</t>
+  </si>
+  <si>
+    <t>university_type</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>country_code</t>
+  </si>
+  <si>
+    <t>state_code</t>
+  </si>
+  <si>
+    <t>city_code</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>website_url</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>agreement_start_date</t>
+  </si>
+  <si>
+    <t>agreement_end_date</t>
+  </si>
+  <si>
+    <t>video_link</t>
+  </si>
+  <si>
+    <t>tuition_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aberystwyth University </t>
+  </si>
+  <si>
+    <t>Academy Of Art University</t>
+  </si>
+  <si>
+    <t>Acadia University</t>
+  </si>
+  <si>
+    <t>Adelphi University</t>
+  </si>
+  <si>
+    <t>IGS QS Partner</t>
+  </si>
+  <si>
+    <t>IGS Partners</t>
+  </si>
+  <si>
+    <t>IGS Shorelight Partner</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>2027-01-24</t>
+  </si>
+  <si>
+    <t>admissions@indoglobalstudies.org</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=N2qemINsv3g</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IiSLdNj_HtI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bjFwELxm0OE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/luNsJdf_sns</t>
+  </si>
+  <si>
+    <t>https://www.aber.ac.uk/en/study-with-us/international/fees-scholarships/?from=globalnav#fee-information-for-international-students</t>
+  </si>
+  <si>
+    <t>https://www.academyart.edu/finances/</t>
+  </si>
+  <si>
+    <t>https://www2.acadiau.ca/student-services/student-accounts/tuition-fees/full-time-student-fees.html</t>
+  </si>
+  <si>
+    <t>https://www.adelphi.edu/aid/tuition-costs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aberystwyth University is a public research university in Aberystwyth, Wales. Aberystwyth was a founding member institution of the former federal University of Wales. The university has over 8,000 students studying across three academic faculties and 17 departments. </t>
+  </si>
+  <si>
+    <t>The Academy of Art University, formerly Academy of Art College and Richard Stephens Academy of Art, is a private for-profit art school in San Francisco, California. It was founded as the Academy of Advertising Art by Richard S. Stephens in 1929.</t>
+  </si>
+  <si>
+    <t>Acadia University is a public, predominantly undergraduate university located in Wolfville, Nova Scotia, Canada, with some graduate programs at the master's level and one at the doctoral level. The enabling legislation consists of the Acadia University Act and the Amended Acadia University Act 2000.</t>
+  </si>
+  <si>
+    <t>Adelphi University is a private university in Garden City, New York. Adelphi also has centers in Downtown Brooklyn, Hudson Valley, and Suffolk County in addition to a virtual, online campus for remote students. It is the oldest institution of higher education in suburban Long Island. As of 2019, it has about 7,859 undergraduate and graduate students.</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>WLS</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>NS</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>Penglais, Aberystwyth SY23 3FL, United Kingdom</t>
+  </si>
+  <si>
+    <t>180 New Montgomery St, San Francisco, CA 94105, United States</t>
+  </si>
+  <si>
+    <t>15 University Ave, Wolfville, NS B4P 2R6, Canada</t>
+  </si>
+  <si>
+    <t>1 South Ave, Garden City, NY 11530, United States</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +203,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,84 +505,219 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" customWidth="1"/>
+    <col min="4" max="4" width="90.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="9" max="9" width="22.5546875" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
+    <col min="13" max="13" width="43.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>partner_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>university_type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>country_code</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>state_code</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>city_code</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>website_url</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>agreement_start_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>agreement_end_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>video_link</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>tuition_url</t>
-        </is>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
